--- a/assets/demo/电信业务数据.xlsx
+++ b/assets/demo/电信业务数据.xlsx
@@ -4,6 +4,8 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="营业厅业务月报" sheetId="1" r:id="rId1"/>
+    <sheet name="用户增长" sheetId="2" r:id="rId2"/>
+    <sheet name="投诉明细" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:E49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,1680 +409,5786 @@
         <v>月份</v>
       </c>
       <c r="C1" t="str">
-        <v>宽带新装(户)</v>
+        <v>宽带新装</v>
       </c>
       <c r="D1" t="str">
-        <v>套餐办理(笔)</v>
+        <v>套餐办理</v>
       </c>
       <c r="E1" t="str">
-        <v>新增用户(户)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>投诉(件)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>投诉率(%)</v>
+        <v>5G升级</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>城东营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B2" t="str">
-        <v>2025-01</v>
+        <v>2025-07</v>
       </c>
       <c r="C2">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="D2">
-        <v>744</v>
+        <v>798</v>
       </c>
       <c r="E2">
-        <v>315</v>
-      </c>
-      <c r="F2">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>0.94</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>城西营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B3" t="str">
-        <v>2025-01</v>
+        <v>2025-07</v>
       </c>
       <c r="C3">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D3">
-        <v>541</v>
+        <v>508</v>
       </c>
       <c r="E3">
-        <v>215</v>
-      </c>
-      <c r="F3">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>1.55</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>城南营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B4" t="str">
-        <v>2025-01</v>
+        <v>2025-07</v>
       </c>
       <c r="C4">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D4">
-        <v>602</v>
+        <v>538</v>
       </c>
       <c r="E4">
-        <v>243</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>0.96</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>城北营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-01</v>
+        <v>2025-07</v>
       </c>
       <c r="C5">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="D5">
-        <v>480</v>
+        <v>509</v>
       </c>
       <c r="E5">
-        <v>200</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>0.81</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>高新区营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-01</v>
+        <v>2025-07</v>
       </c>
       <c r="C6">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="D6">
-        <v>576</v>
+        <v>632</v>
       </c>
       <c r="E6">
-        <v>261</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>0.77</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>老城口营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-01</v>
+        <v>2025-07</v>
       </c>
       <c r="C7">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D7">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="E7">
-        <v>140</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>1.44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>城东营业厅</v>
+        <v>滨江厅</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-02</v>
+        <v>2025-07</v>
       </c>
       <c r="C8">
-        <v>465</v>
+        <v>287</v>
       </c>
       <c r="D8">
-        <v>719</v>
+        <v>486</v>
       </c>
       <c r="E8">
-        <v>300</v>
-      </c>
-      <c r="F8">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>0.93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>城西营业厅</v>
+        <v>中心厅</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-02</v>
+        <v>2025-07</v>
       </c>
       <c r="C9">
-        <v>294</v>
+        <v>378</v>
       </c>
       <c r="D9">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E9">
         <v>177</v>
       </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
-      <c r="G9">
-        <v>2.39</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>城南营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-02</v>
+        <v>2025-08</v>
       </c>
       <c r="C10">
-        <v>356</v>
+        <v>474</v>
       </c>
       <c r="D10">
-        <v>585</v>
+        <v>833</v>
       </c>
       <c r="E10">
-        <v>256</v>
-      </c>
-      <c r="F10">
-        <v>8</v>
-      </c>
-      <c r="G10">
-        <v>0.85</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>城北营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-02</v>
+        <v>2025-08</v>
       </c>
       <c r="C11">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="D11">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="E11">
-        <v>183</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>0.6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>高新区营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B12" t="str">
-        <v>2025-02</v>
+        <v>2025-08</v>
       </c>
       <c r="C12">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="D12">
-        <v>667</v>
+        <v>551</v>
       </c>
       <c r="E12">
-        <v>277</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="G12">
-        <v>0.72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>老城口营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B13" t="str">
-        <v>2025-02</v>
+        <v>2025-08</v>
       </c>
       <c r="C13">
-        <v>212</v>
+        <v>283</v>
       </c>
       <c r="D13">
-        <v>394</v>
+        <v>495</v>
       </c>
       <c r="E13">
-        <v>129</v>
-      </c>
-      <c r="F13">
-        <v>7</v>
-      </c>
-      <c r="G13">
-        <v>1.16</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>城东营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B14" t="str">
-        <v>2025-03</v>
+        <v>2025-08</v>
       </c>
       <c r="C14">
-        <v>502</v>
+        <v>426</v>
       </c>
       <c r="D14">
-        <v>941</v>
+        <v>738</v>
       </c>
       <c r="E14">
-        <v>339</v>
-      </c>
-      <c r="F14">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>0.76</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>城西营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B15" t="str">
-        <v>2025-03</v>
+        <v>2025-08</v>
       </c>
       <c r="C15">
-        <v>294</v>
+        <v>164</v>
       </c>
       <c r="D15">
-        <v>480</v>
+        <v>291</v>
       </c>
       <c r="E15">
-        <v>199</v>
-      </c>
-      <c r="F15">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>2.07</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>城南营业厅</v>
+        <v>滨江厅</v>
       </c>
       <c r="B16" t="str">
-        <v>2025-03</v>
+        <v>2025-08</v>
       </c>
       <c r="C16">
-        <v>379</v>
+        <v>301</v>
       </c>
       <c r="D16">
-        <v>688</v>
+        <v>472</v>
       </c>
       <c r="E16">
-        <v>242</v>
-      </c>
-      <c r="F16">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>1.22</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>城北营业厅</v>
+        <v>中心厅</v>
       </c>
       <c r="B17" t="str">
-        <v>2025-03</v>
+        <v>2025-08</v>
       </c>
       <c r="C17">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="D17">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="E17">
-        <v>231</v>
-      </c>
-      <c r="F17">
-        <v>7</v>
-      </c>
-      <c r="G17">
-        <v>0.72</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>高新区营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B18" t="str">
-        <v>2025-03</v>
+        <v>2025-09</v>
       </c>
       <c r="C18">
-        <v>472</v>
+        <v>443</v>
       </c>
       <c r="D18">
-        <v>778</v>
+        <v>846</v>
       </c>
       <c r="E18">
-        <v>291</v>
-      </c>
-      <c r="F18">
-        <v>8</v>
-      </c>
-      <c r="G18">
-        <v>0.64</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>老城口营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B19" t="str">
-        <v>2025-03</v>
+        <v>2025-09</v>
       </c>
       <c r="C19">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="D19">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="E19">
-        <v>124</v>
-      </c>
-      <c r="F19">
-        <v>7</v>
-      </c>
-      <c r="G19">
-        <v>1.13</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>城东营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B20" t="str">
-        <v>2025-04</v>
+        <v>2025-09</v>
       </c>
       <c r="C20">
-        <v>555</v>
+        <v>298</v>
       </c>
       <c r="D20">
-        <v>953</v>
+        <v>485</v>
       </c>
       <c r="E20">
-        <v>307</v>
-      </c>
-      <c r="F20">
-        <v>15</v>
-      </c>
-      <c r="G20">
-        <v>0.99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>城西营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B21" t="str">
-        <v>2025-04</v>
+        <v>2025-09</v>
       </c>
       <c r="C21">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D21">
-        <v>478</v>
+        <v>531</v>
       </c>
       <c r="E21">
-        <v>160</v>
-      </c>
-      <c r="F21">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>2.02</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>城南营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B22" t="str">
-        <v>2025-04</v>
+        <v>2025-09</v>
       </c>
       <c r="C22">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="D22">
-        <v>684</v>
+        <v>630</v>
       </c>
       <c r="E22">
-        <v>219</v>
-      </c>
-      <c r="F22">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>0.99</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>城北营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B23" t="str">
-        <v>2025-04</v>
+        <v>2025-09</v>
       </c>
       <c r="C23">
-        <v>397</v>
+        <v>153</v>
       </c>
       <c r="D23">
-        <v>638</v>
+        <v>244</v>
       </c>
       <c r="E23">
-        <v>217</v>
-      </c>
-      <c r="F23">
-        <v>8</v>
-      </c>
-      <c r="G23">
-        <v>0.77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>高新区营业厅</v>
+        <v>滨江厅</v>
       </c>
       <c r="B24" t="str">
-        <v>2025-04</v>
+        <v>2025-09</v>
       </c>
       <c r="C24">
-        <v>509</v>
+        <v>268</v>
       </c>
       <c r="D24">
-        <v>957</v>
+        <v>537</v>
       </c>
       <c r="E24">
-        <v>326</v>
-      </c>
-      <c r="F24">
-        <v>7</v>
-      </c>
-      <c r="G24">
-        <v>0.48</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>老城口营业厅</v>
+        <v>中心厅</v>
       </c>
       <c r="B25" t="str">
-        <v>2025-04</v>
+        <v>2025-09</v>
       </c>
       <c r="C25">
-        <v>222</v>
+        <v>349</v>
       </c>
       <c r="D25">
-        <v>394</v>
+        <v>571</v>
       </c>
       <c r="E25">
-        <v>136</v>
-      </c>
-      <c r="F25">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>1.62</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>城东营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B26" t="str">
-        <v>2025-05</v>
+        <v>2025-10</v>
       </c>
       <c r="C26">
-        <v>558</v>
+        <v>452</v>
       </c>
       <c r="D26">
-        <v>965</v>
+        <v>709</v>
       </c>
       <c r="E26">
-        <v>304</v>
-      </c>
-      <c r="F26">
-        <v>15</v>
-      </c>
-      <c r="G26">
-        <v>0.98</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>城西营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B27" t="str">
-        <v>2025-05</v>
+        <v>2025-10</v>
       </c>
       <c r="C27">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D27">
-        <v>463</v>
+        <v>418</v>
       </c>
       <c r="E27">
-        <v>161</v>
-      </c>
-      <c r="F27">
-        <v>17</v>
-      </c>
-      <c r="G27">
-        <v>2.34</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>城南营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B28" t="str">
-        <v>2025-05</v>
+        <v>2025-10</v>
       </c>
       <c r="C28">
-        <v>436</v>
+        <v>293</v>
       </c>
       <c r="D28">
-        <v>750</v>
+        <v>452</v>
       </c>
       <c r="E28">
-        <v>265</v>
-      </c>
-      <c r="F28">
-        <v>13</v>
-      </c>
-      <c r="G28">
-        <v>1.1</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>城北营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B29" t="str">
-        <v>2025-05</v>
+        <v>2025-10</v>
       </c>
       <c r="C29">
-        <v>396</v>
+        <v>254</v>
       </c>
       <c r="D29">
-        <v>745</v>
+        <v>414</v>
       </c>
       <c r="E29">
-        <v>260</v>
-      </c>
-      <c r="F29">
-        <v>9</v>
-      </c>
-      <c r="G29">
-        <v>0.79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>高新区营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B30" t="str">
-        <v>2025-05</v>
+        <v>2025-10</v>
       </c>
       <c r="C30">
-        <v>575</v>
+        <v>379</v>
       </c>
       <c r="D30">
-        <v>884</v>
+        <v>587</v>
       </c>
       <c r="E30">
-        <v>335</v>
-      </c>
-      <c r="F30">
-        <v>10</v>
-      </c>
-      <c r="G30">
-        <v>0.69</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>老城口营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B31" t="str">
-        <v>2025-05</v>
+        <v>2025-10</v>
       </c>
       <c r="C31">
-        <v>233</v>
+        <v>103</v>
       </c>
       <c r="D31">
-        <v>399</v>
+        <v>215</v>
       </c>
       <c r="E31">
-        <v>142</v>
-      </c>
-      <c r="F31">
-        <v>9</v>
-      </c>
-      <c r="G31">
-        <v>1.42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>城东营业厅</v>
+        <v>滨江厅</v>
       </c>
       <c r="B32" t="str">
-        <v>2025-06</v>
+        <v>2025-10</v>
       </c>
       <c r="C32">
-        <v>632</v>
+        <v>260</v>
       </c>
       <c r="D32">
-        <v>1049</v>
+        <v>473</v>
       </c>
       <c r="E32">
-        <v>363</v>
-      </c>
-      <c r="F32">
-        <v>13</v>
-      </c>
-      <c r="G32">
-        <v>0.77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>城西营业厅</v>
+        <v>中心厅</v>
       </c>
       <c r="B33" t="str">
-        <v>2025-06</v>
+        <v>2025-10</v>
       </c>
       <c r="C33">
-        <v>217</v>
+        <v>333</v>
       </c>
       <c r="D33">
-        <v>380</v>
+        <v>485</v>
       </c>
       <c r="E33">
-        <v>135</v>
-      </c>
-      <c r="F33">
-        <v>10</v>
-      </c>
-      <c r="G33">
-        <v>1.68</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>城南营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B34" t="str">
-        <v>2025-06</v>
+        <v>2025-11</v>
       </c>
       <c r="C34">
-        <v>439</v>
+        <v>509</v>
       </c>
       <c r="D34">
-        <v>785</v>
+        <v>851</v>
       </c>
       <c r="E34">
-        <v>223</v>
-      </c>
-      <c r="F34">
-        <v>12</v>
-      </c>
-      <c r="G34">
-        <v>0.98</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>城北营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B35" t="str">
-        <v>2025-06</v>
+        <v>2025-11</v>
       </c>
       <c r="C35">
-        <v>421</v>
+        <v>258</v>
       </c>
       <c r="D35">
-        <v>709</v>
+        <v>441</v>
       </c>
       <c r="E35">
-        <v>271</v>
-      </c>
-      <c r="F35">
-        <v>10</v>
-      </c>
-      <c r="G35">
-        <v>0.88</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>高新区营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B36" t="str">
-        <v>2025-06</v>
+        <v>2025-11</v>
       </c>
       <c r="C36">
-        <v>521</v>
+        <v>312</v>
       </c>
       <c r="D36">
-        <v>979</v>
+        <v>523</v>
       </c>
       <c r="E36">
-        <v>340</v>
-      </c>
-      <c r="F36">
-        <v>11</v>
-      </c>
-      <c r="G36">
-        <v>0.73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>老城口营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B37" t="str">
-        <v>2025-06</v>
+        <v>2025-11</v>
       </c>
       <c r="C37">
-        <v>227</v>
+        <v>277</v>
       </c>
       <c r="D37">
-        <v>360</v>
+        <v>510</v>
       </c>
       <c r="E37">
-        <v>123</v>
-      </c>
-      <c r="F37">
-        <v>10</v>
-      </c>
-      <c r="G37">
-        <v>1.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>城东营业厅</v>
+        <v>高新区厅</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C38">
+        <v>342</v>
+      </c>
+      <c r="D38">
+        <v>695</v>
+      </c>
+      <c r="E38">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C39">
+        <v>89</v>
+      </c>
+      <c r="D39">
+        <v>165</v>
+      </c>
+      <c r="E39">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C40">
+        <v>281</v>
+      </c>
+      <c r="D40">
+        <v>417</v>
+      </c>
+      <c r="E40">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C41">
+        <v>335</v>
+      </c>
+      <c r="D41">
+        <v>568</v>
+      </c>
+      <c r="E41">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C42">
+        <v>575</v>
+      </c>
+      <c r="D42">
+        <v>924</v>
+      </c>
+      <c r="E42">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C43">
+        <v>262</v>
+      </c>
+      <c r="D43">
+        <v>440</v>
+      </c>
+      <c r="E43">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C44">
+        <v>355</v>
+      </c>
+      <c r="D44">
+        <v>508</v>
+      </c>
+      <c r="E44">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C45">
+        <v>320</v>
+      </c>
+      <c r="D45">
+        <v>554</v>
+      </c>
+      <c r="E45">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C46">
+        <v>396</v>
+      </c>
+      <c r="D46">
+        <v>677</v>
+      </c>
+      <c r="E46">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C47">
+        <v>95</v>
+      </c>
+      <c r="D47">
+        <v>154</v>
+      </c>
+      <c r="E47">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C48">
+        <v>321</v>
+      </c>
+      <c r="D48">
+        <v>465</v>
+      </c>
+      <c r="E48">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C49">
+        <v>346</v>
+      </c>
+      <c r="D49">
+        <v>553</v>
+      </c>
+      <c r="E49">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E49"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E49"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>营业厅</v>
+      </c>
+      <c r="B1" t="str">
+        <v>月份</v>
+      </c>
+      <c r="C1" t="str">
+        <v>新增用户</v>
+      </c>
+      <c r="D1" t="str">
+        <v>流失用户</v>
+      </c>
+      <c r="E1" t="str">
+        <v>净增</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C2">
+        <v>288</v>
+      </c>
+      <c r="D2">
+        <v>19</v>
+      </c>
+      <c r="E2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C3">
+        <v>219</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C4">
+        <v>189</v>
+      </c>
+      <c r="D4">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C5">
+        <v>165</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C6">
+        <v>243</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C7">
+        <v>122</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C8">
+        <v>209</v>
+      </c>
+      <c r="D8">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C9">
+        <v>233</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C10">
+        <v>274</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C11">
+        <v>213</v>
+      </c>
+      <c r="D11">
+        <v>19</v>
+      </c>
+      <c r="E11">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C12">
+        <v>241</v>
+      </c>
+      <c r="D12">
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C13">
+        <v>186</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C14">
+        <v>283</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C15">
+        <v>124</v>
+      </c>
+      <c r="D15">
+        <v>19</v>
+      </c>
+      <c r="E15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C16">
+        <v>207</v>
+      </c>
+      <c r="D16">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C17">
+        <v>255</v>
+      </c>
+      <c r="D17">
+        <v>18</v>
+      </c>
+      <c r="E17">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C18">
+        <v>282</v>
+      </c>
+      <c r="D18">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C19">
+        <v>194</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C20">
+        <v>217</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C21">
+        <v>203</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C22">
+        <v>271</v>
+      </c>
+      <c r="D22">
+        <v>18</v>
+      </c>
+      <c r="E22">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C23">
+        <v>90</v>
+      </c>
+      <c r="D23">
+        <v>15</v>
+      </c>
+      <c r="E23">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C24">
+        <v>218</v>
+      </c>
+      <c r="D24">
+        <v>17</v>
+      </c>
+      <c r="E24">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C25">
+        <v>243</v>
+      </c>
+      <c r="D25">
+        <v>17</v>
+      </c>
+      <c r="E25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C26">
+        <v>362</v>
+      </c>
+      <c r="D26">
+        <v>21</v>
+      </c>
+      <c r="E26">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C27">
+        <v>186</v>
+      </c>
+      <c r="D27">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C28">
+        <v>214</v>
+      </c>
+      <c r="D28">
+        <v>17</v>
+      </c>
+      <c r="E28">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C29">
+        <v>222</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C30">
+        <v>242</v>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C31">
+        <v>83</v>
+      </c>
+      <c r="D31">
+        <v>13</v>
+      </c>
+      <c r="E31">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C32">
+        <v>176</v>
+      </c>
+      <c r="D32">
+        <v>14</v>
+      </c>
+      <c r="E32">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C33">
+        <v>236</v>
+      </c>
+      <c r="D33">
+        <v>17</v>
+      </c>
+      <c r="E33">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C34">
+        <v>349</v>
+      </c>
+      <c r="D34">
+        <v>21</v>
+      </c>
+      <c r="E34">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C35">
+        <v>169</v>
+      </c>
+      <c r="D35">
+        <v>16</v>
+      </c>
+      <c r="E35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C36">
+        <v>215</v>
+      </c>
+      <c r="D36">
+        <v>20</v>
+      </c>
+      <c r="E36">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C37">
+        <v>236</v>
+      </c>
+      <c r="D37">
+        <v>17</v>
+      </c>
+      <c r="E37">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C38">
+        <v>314</v>
+      </c>
+      <c r="D38">
+        <v>17</v>
+      </c>
+      <c r="E38">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C39">
+        <v>69</v>
+      </c>
+      <c r="D39">
+        <v>15</v>
+      </c>
+      <c r="E39">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C40">
+        <v>217</v>
+      </c>
+      <c r="D40">
+        <v>18</v>
+      </c>
+      <c r="E40">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C41">
+        <v>253</v>
+      </c>
+      <c r="D41">
+        <v>15</v>
+      </c>
+      <c r="E41">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C42">
+        <v>447</v>
+      </c>
+      <c r="D42">
+        <v>23</v>
+      </c>
+      <c r="E42">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C43">
+        <v>185</v>
+      </c>
+      <c r="D43">
+        <v>21</v>
+      </c>
+      <c r="E43">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C44">
+        <v>221</v>
+      </c>
+      <c r="D44">
+        <v>17</v>
+      </c>
+      <c r="E44">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C45">
+        <v>247</v>
+      </c>
+      <c r="D45">
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C46">
+        <v>257</v>
+      </c>
+      <c r="D46">
+        <v>19</v>
+      </c>
+      <c r="E46">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C47">
+        <v>65</v>
+      </c>
+      <c r="D47">
+        <v>14</v>
+      </c>
+      <c r="E47">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C48">
+        <v>173</v>
+      </c>
+      <c r="D48">
+        <v>19</v>
+      </c>
+      <c r="E48">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C49">
+        <v>268</v>
+      </c>
+      <c r="D49">
+        <v>21</v>
+      </c>
+      <c r="E49">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E49"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E241"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>营业厅</v>
+      </c>
+      <c r="B1" t="str">
+        <v>月份</v>
+      </c>
+      <c r="C1" t="str">
+        <v>投诉类别</v>
+      </c>
+      <c r="D1" t="str">
+        <v>投诉量</v>
+      </c>
+      <c r="E1" t="str">
+        <v>处理时长</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C2" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C3" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C4" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C5" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C6" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C7" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C8" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C9" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C10" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C11" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C12" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C13" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C14" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C15" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C16" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C17" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
+      </c>
+      <c r="E17">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C18" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C19" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C20" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C21" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C22" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C23" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D23">
+        <v>11</v>
+      </c>
+      <c r="E23">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C24" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C25" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C26" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C27" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D27">
+        <v>17</v>
+      </c>
+      <c r="E27">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C28" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C29" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C30" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C31" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C32" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C33" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D33">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C34" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D34">
+        <v>5</v>
+      </c>
+      <c r="E34">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C35" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C36" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="C37" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D37">
+        <v>11</v>
+      </c>
+      <c r="E37">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>中心厅</v>
       </c>
       <c r="B38" t="str">
         <v>2025-07</v>
       </c>
-      <c r="C38">
-        <v>618</v>
+      <c r="C38" t="str">
+        <v>网络质量</v>
       </c>
       <c r="D38">
-        <v>1068</v>
+        <v>11</v>
       </c>
       <c r="E38">
-        <v>344</v>
-      </c>
-      <c r="F38">
-        <v>16</v>
-      </c>
-      <c r="G38">
-        <v>0.95</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>城西营业厅</v>
+        <v>中心厅</v>
       </c>
       <c r="B39" t="str">
         <v>2025-07</v>
       </c>
-      <c r="C39">
-        <v>187</v>
+      <c r="C39" t="str">
+        <v>资费争议</v>
       </c>
       <c r="D39">
-        <v>347</v>
+        <v>6</v>
       </c>
       <c r="E39">
-        <v>130</v>
-      </c>
-      <c r="F39">
-        <v>11</v>
-      </c>
-      <c r="G39">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>城南营业厅</v>
+        <v>中心厅</v>
       </c>
       <c r="B40" t="str">
         <v>2025-07</v>
       </c>
-      <c r="C40">
-        <v>389</v>
+      <c r="C40" t="str">
+        <v>业务办理</v>
       </c>
       <c r="D40">
-        <v>692</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>232</v>
-      </c>
-      <c r="F40">
-        <v>10</v>
-      </c>
-      <c r="G40">
-        <v>0.93</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>城北营业厅</v>
+        <v>中心厅</v>
       </c>
       <c r="B41" t="str">
         <v>2025-07</v>
       </c>
-      <c r="C41">
-        <v>429</v>
+      <c r="C41" t="str">
+        <v>其他</v>
       </c>
       <c r="D41">
-        <v>725</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>265</v>
-      </c>
-      <c r="F41">
-        <v>10</v>
-      </c>
-      <c r="G41">
-        <v>0.87</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>高新区营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B42" t="str">
-        <v>2025-07</v>
-      </c>
-      <c r="C42">
-        <v>553</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C42" t="str">
+        <v>装维服务</v>
       </c>
       <c r="D42">
-        <v>926</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>368</v>
-      </c>
-      <c r="F42">
-        <v>11</v>
-      </c>
-      <c r="G42">
-        <v>0.74</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>老城口营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B43" t="str">
-        <v>2025-07</v>
-      </c>
-      <c r="C43">
-        <v>216</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C43" t="str">
+        <v>网络质量</v>
       </c>
       <c r="D43">
-        <v>384</v>
+        <v>11</v>
       </c>
       <c r="E43">
-        <v>120</v>
-      </c>
-      <c r="F43">
-        <v>10</v>
-      </c>
-      <c r="G43">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>城东营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B44" t="str">
         <v>2025-08</v>
       </c>
-      <c r="C44">
-        <v>556</v>
+      <c r="C44" t="str">
+        <v>资费争议</v>
       </c>
       <c r="D44">
-        <v>1098</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>360</v>
-      </c>
-      <c r="F44">
-        <v>14</v>
-      </c>
-      <c r="G44">
-        <v>0.85</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>城西营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B45" t="str">
         <v>2025-08</v>
       </c>
-      <c r="C45">
-        <v>151</v>
+      <c r="C45" t="str">
+        <v>业务办理</v>
       </c>
       <c r="D45">
-        <v>252</v>
+        <v>8</v>
       </c>
       <c r="E45">
-        <v>96</v>
-      </c>
-      <c r="F45">
-        <v>8</v>
-      </c>
-      <c r="G45">
-        <v>1.99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>城南营业厅</v>
+        <v>城东厅</v>
       </c>
       <c r="B46" t="str">
         <v>2025-08</v>
       </c>
-      <c r="C46">
-        <v>381</v>
+      <c r="C46" t="str">
+        <v>其他</v>
       </c>
       <c r="D46">
-        <v>677</v>
+        <v>7</v>
       </c>
       <c r="E46">
-        <v>253</v>
-      </c>
-      <c r="F46">
-        <v>12</v>
-      </c>
-      <c r="G46">
-        <v>1.13</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>城北营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B47" t="str">
         <v>2025-08</v>
       </c>
-      <c r="C47">
-        <v>446</v>
+      <c r="C47" t="str">
+        <v>装维服务</v>
       </c>
       <c r="D47">
-        <v>700</v>
+        <v>13</v>
       </c>
       <c r="E47">
-        <v>262</v>
-      </c>
-      <c r="F47">
-        <v>9</v>
-      </c>
-      <c r="G47">
-        <v>0.79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>高新区营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B48" t="str">
         <v>2025-08</v>
       </c>
-      <c r="C48">
-        <v>529</v>
+      <c r="C48" t="str">
+        <v>网络质量</v>
       </c>
       <c r="D48">
-        <v>994</v>
+        <v>8</v>
       </c>
       <c r="E48">
-        <v>366</v>
-      </c>
-      <c r="F48">
-        <v>8</v>
-      </c>
-      <c r="G48">
-        <v>0.53</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>老城口营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B49" t="str">
         <v>2025-08</v>
       </c>
-      <c r="C49">
-        <v>183</v>
+      <c r="C49" t="str">
+        <v>资费争议</v>
       </c>
       <c r="D49">
-        <v>346</v>
+        <v>4</v>
       </c>
       <c r="E49">
-        <v>113</v>
-      </c>
-      <c r="F49">
-        <v>9</v>
-      </c>
-      <c r="G49">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>城东营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B50" t="str">
-        <v>2025-09</v>
-      </c>
-      <c r="C50">
-        <v>579</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C50" t="str">
+        <v>业务办理</v>
       </c>
       <c r="D50">
-        <v>1023</v>
+        <v>5</v>
       </c>
       <c r="E50">
-        <v>351</v>
-      </c>
-      <c r="F50">
-        <v>16</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>城西营业厅</v>
+        <v>城西厅</v>
       </c>
       <c r="B51" t="str">
-        <v>2025-09</v>
-      </c>
-      <c r="C51">
-        <v>123</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C51" t="str">
+        <v>其他</v>
       </c>
       <c r="D51">
-        <v>237</v>
+        <v>5</v>
       </c>
       <c r="E51">
-        <v>95</v>
-      </c>
-      <c r="F51">
-        <v>7</v>
-      </c>
-      <c r="G51">
-        <v>1.94</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>城南营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B52" t="str">
-        <v>2025-09</v>
-      </c>
-      <c r="C52">
-        <v>374</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C52" t="str">
+        <v>装维服务</v>
       </c>
       <c r="D52">
-        <v>653</v>
+        <v>9</v>
       </c>
       <c r="E52">
-        <v>244</v>
-      </c>
-      <c r="F52">
-        <v>12</v>
-      </c>
-      <c r="G52">
-        <v>1.17</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>城北营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B53" t="str">
-        <v>2025-09</v>
-      </c>
-      <c r="C53">
-        <v>435</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C53" t="str">
+        <v>网络质量</v>
       </c>
       <c r="D53">
-        <v>697</v>
+        <v>8</v>
       </c>
       <c r="E53">
-        <v>285</v>
-      </c>
-      <c r="F53">
-        <v>10</v>
-      </c>
-      <c r="G53">
-        <v>0.88</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>高新区营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B54" t="str">
-        <v>2025-09</v>
-      </c>
-      <c r="C54">
-        <v>490</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C54" t="str">
+        <v>资费争议</v>
       </c>
       <c r="D54">
-        <v>879</v>
+        <v>5</v>
       </c>
       <c r="E54">
-        <v>359</v>
-      </c>
-      <c r="F54">
-        <v>10</v>
-      </c>
-      <c r="G54">
-        <v>0.73</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>老城口营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B55" t="str">
-        <v>2025-09</v>
-      </c>
-      <c r="C55">
-        <v>173</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C55" t="str">
+        <v>业务办理</v>
       </c>
       <c r="D55">
-        <v>288</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>111</v>
-      </c>
-      <c r="F55">
-        <v>6</v>
-      </c>
-      <c r="G55">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>城东营业厅</v>
+        <v>城南厅</v>
       </c>
       <c r="B56" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="C56">
-        <v>548</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C56" t="str">
+        <v>其他</v>
       </c>
       <c r="D56">
-        <v>940</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>446</v>
-      </c>
-      <c r="F56">
-        <v>11</v>
-      </c>
-      <c r="G56">
-        <v>0.74</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>城西营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B57" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="C57">
-        <v>91</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C57" t="str">
+        <v>装维服务</v>
       </c>
       <c r="D57">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="E57">
-        <v>83</v>
-      </c>
-      <c r="F57">
-        <v>5</v>
-      </c>
-      <c r="G57">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>城南营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B58" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="C58">
-        <v>340</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C58" t="str">
+        <v>网络质量</v>
       </c>
       <c r="D58">
-        <v>553</v>
+        <v>8</v>
       </c>
       <c r="E58">
-        <v>289</v>
-      </c>
-      <c r="F58">
-        <v>11</v>
-      </c>
-      <c r="G58">
-        <v>1.23</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>城北营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B59" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="C59">
-        <v>427</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C59" t="str">
+        <v>资费争议</v>
       </c>
       <c r="D59">
-        <v>777</v>
+        <v>5</v>
       </c>
       <c r="E59">
-        <v>291</v>
-      </c>
-      <c r="F59">
-        <v>10</v>
-      </c>
-      <c r="G59">
-        <v>0.83</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>高新区营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B60" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="C60">
-        <v>475</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C60" t="str">
+        <v>业务办理</v>
       </c>
       <c r="D60">
-        <v>856</v>
+        <v>4</v>
       </c>
       <c r="E60">
-        <v>377</v>
-      </c>
-      <c r="F60">
-        <v>8</v>
-      </c>
-      <c r="G60">
-        <v>0.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>老城口营业厅</v>
+        <v>城北厅</v>
       </c>
       <c r="B61" t="str">
-        <v>2025-10</v>
-      </c>
-      <c r="C61">
-        <v>143</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C61" t="str">
+        <v>其他</v>
       </c>
       <c r="D61">
-        <v>241</v>
+        <v>4</v>
       </c>
       <c r="E61">
-        <v>124</v>
-      </c>
-      <c r="F61">
-        <v>5</v>
-      </c>
-      <c r="G61">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>城东营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B62" t="str">
-        <v>2025-11</v>
-      </c>
-      <c r="C62">
-        <v>506</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C62" t="str">
+        <v>装维服务</v>
       </c>
       <c r="D62">
-        <v>928</v>
+        <v>9</v>
       </c>
       <c r="E62">
-        <v>386</v>
-      </c>
-      <c r="F62">
-        <v>15</v>
-      </c>
-      <c r="G62">
-        <v>1.05</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>城西营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B63" t="str">
-        <v>2025-11</v>
-      </c>
-      <c r="C63">
-        <v>77</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C63" t="str">
+        <v>网络质量</v>
       </c>
       <c r="D63">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="E63">
-        <v>54</v>
-      </c>
-      <c r="F63">
-        <v>5</v>
-      </c>
-      <c r="G63">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>城南营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B64" t="str">
-        <v>2025-11</v>
-      </c>
-      <c r="C64">
-        <v>361</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C64" t="str">
+        <v>资费争议</v>
       </c>
       <c r="D64">
-        <v>555</v>
+        <v>6</v>
       </c>
       <c r="E64">
-        <v>282</v>
-      </c>
-      <c r="F64">
-        <v>9</v>
-      </c>
-      <c r="G64">
-        <v>0.98</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>城北营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B65" t="str">
-        <v>2025-11</v>
-      </c>
-      <c r="C65">
-        <v>387</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C65" t="str">
+        <v>业务办理</v>
       </c>
       <c r="D65">
-        <v>719</v>
+        <v>8</v>
       </c>
       <c r="E65">
-        <v>301</v>
-      </c>
-      <c r="F65">
-        <v>8</v>
-      </c>
-      <c r="G65">
-        <v>0.72</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>高新区营业厅</v>
+        <v>高新区厅</v>
       </c>
       <c r="B66" t="str">
-        <v>2025-11</v>
-      </c>
-      <c r="C66">
-        <v>521</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C66" t="str">
+        <v>其他</v>
       </c>
       <c r="D66">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>360</v>
-      </c>
-      <c r="F66">
-        <v>9</v>
-      </c>
-      <c r="G66">
-        <v>0.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>老城口营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B67" t="str">
-        <v>2025-11</v>
-      </c>
-      <c r="C67">
-        <v>155</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C67" t="str">
+        <v>装维服务</v>
       </c>
       <c r="D67">
-        <v>273</v>
+        <v>13</v>
       </c>
       <c r="E67">
-        <v>105</v>
-      </c>
-      <c r="F67">
-        <v>6</v>
-      </c>
-      <c r="G67">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>城东营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B68" t="str">
-        <v>2025-12</v>
-      </c>
-      <c r="C68">
-        <v>573</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C68" t="str">
+        <v>网络质量</v>
       </c>
       <c r="D68">
-        <v>1063</v>
+        <v>9</v>
       </c>
       <c r="E68">
-        <v>398</v>
-      </c>
-      <c r="F68">
-        <v>12</v>
-      </c>
-      <c r="G68">
-        <v>0.73</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>城西营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B69" t="str">
-        <v>2025-12</v>
-      </c>
-      <c r="C69">
-        <v>56</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C69" t="str">
+        <v>资费争议</v>
       </c>
       <c r="D69">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="E69">
-        <v>45</v>
-      </c>
-      <c r="F69">
-        <v>3</v>
-      </c>
-      <c r="G69">
-        <v>1.96</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>城南营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B70" t="str">
-        <v>2025-12</v>
-      </c>
-      <c r="C70">
-        <v>347</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C70" t="str">
+        <v>业务办理</v>
       </c>
       <c r="D70">
-        <v>580</v>
+        <v>2</v>
       </c>
       <c r="E70">
-        <v>244</v>
-      </c>
-      <c r="F70">
-        <v>10</v>
-      </c>
-      <c r="G70">
-        <v>1.08</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>城北营业厅</v>
+        <v>老城厅</v>
       </c>
       <c r="B71" t="str">
-        <v>2025-12</v>
-      </c>
-      <c r="C71">
-        <v>478</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C71" t="str">
+        <v>其他</v>
       </c>
       <c r="D71">
-        <v>717</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>344</v>
-      </c>
-      <c r="F71">
-        <v>10</v>
-      </c>
-      <c r="G71">
-        <v>0.84</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>高新区营业厅</v>
+        <v>滨江厅</v>
       </c>
       <c r="B72" t="str">
-        <v>2025-12</v>
-      </c>
-      <c r="C72">
-        <v>581</v>
+        <v>2025-08</v>
+      </c>
+      <c r="C72" t="str">
+        <v>装维服务</v>
       </c>
       <c r="D72">
-        <v>1021</v>
+        <v>8</v>
       </c>
       <c r="E72">
-        <v>438</v>
-      </c>
-      <c r="F72">
-        <v>10</v>
-      </c>
-      <c r="G72">
-        <v>0.62</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>老城口营业厅</v>
+        <v>滨江厅</v>
       </c>
       <c r="B73" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C73" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D73">
+        <v>6</v>
+      </c>
+      <c r="E73">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C74" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C75" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C76" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D76">
+        <v>5</v>
+      </c>
+      <c r="E76">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C77" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D77">
+        <v>8</v>
+      </c>
+      <c r="E77">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C78" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D78">
+        <v>11</v>
+      </c>
+      <c r="E78">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C79" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D79">
+        <v>6</v>
+      </c>
+      <c r="E79">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C80" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="C81" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C82" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C83" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D83">
+        <v>14</v>
+      </c>
+      <c r="E83">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C84" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+      <c r="E84">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C85" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D85">
+        <v>7</v>
+      </c>
+      <c r="E85">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C86" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D86">
+        <v>8</v>
+      </c>
+      <c r="E86">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C87" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D87">
+        <v>9</v>
+      </c>
+      <c r="E87">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C88" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D88">
+        <v>9</v>
+      </c>
+      <c r="E88">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C89" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D89">
+        <v>5</v>
+      </c>
+      <c r="E89">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C90" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D90">
+        <v>4</v>
+      </c>
+      <c r="E90">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C91" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D91">
+        <v>5</v>
+      </c>
+      <c r="E91">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C92" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D92">
+        <v>10</v>
+      </c>
+      <c r="E92">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C93" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D93">
+        <v>7</v>
+      </c>
+      <c r="E93">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C94" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D94">
+        <v>4</v>
+      </c>
+      <c r="E94">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C95" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D95">
+        <v>5</v>
+      </c>
+      <c r="E95">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C96" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D96">
+        <v>5</v>
+      </c>
+      <c r="E96">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C97" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D97">
+        <v>8</v>
+      </c>
+      <c r="E97">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C98" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D98">
+        <v>9</v>
+      </c>
+      <c r="E98">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C99" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D99">
+        <v>5</v>
+      </c>
+      <c r="E99">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C100" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D100">
+        <v>5</v>
+      </c>
+      <c r="E100">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C101" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D101">
+        <v>6</v>
+      </c>
+      <c r="E101">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C102" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D102">
+        <v>8</v>
+      </c>
+      <c r="E102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C103" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D103">
+        <v>10</v>
+      </c>
+      <c r="E103">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C104" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D104">
+        <v>5</v>
+      </c>
+      <c r="E104">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C105" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D105">
+        <v>5</v>
+      </c>
+      <c r="E105">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C106" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D106">
+        <v>8</v>
+      </c>
+      <c r="E106">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C107" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D107">
+        <v>12</v>
+      </c>
+      <c r="E107">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C108" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D108">
+        <v>8</v>
+      </c>
+      <c r="E108">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C109" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+      <c r="E109">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C110" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C111" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+      <c r="E111">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C112" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D112">
+        <v>8</v>
+      </c>
+      <c r="E112">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C113" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D113">
+        <v>8</v>
+      </c>
+      <c r="E113">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C114" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D114">
+        <v>4</v>
+      </c>
+      <c r="E114">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C115" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+      <c r="E115">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C116" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D116">
+        <v>4</v>
+      </c>
+      <c r="E116">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C117" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D117">
+        <v>11</v>
+      </c>
+      <c r="E117">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C118" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D118">
+        <v>9</v>
+      </c>
+      <c r="E118">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C119" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D119">
+        <v>6</v>
+      </c>
+      <c r="E119">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C120" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D120">
+        <v>6</v>
+      </c>
+      <c r="E120">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="C121" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D121">
+        <v>6</v>
+      </c>
+      <c r="E121">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C122" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D122">
+        <v>5</v>
+      </c>
+      <c r="E122">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C123" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D123">
+        <v>13</v>
+      </c>
+      <c r="E123">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C124" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D124">
+        <v>6</v>
+      </c>
+      <c r="E124">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C125" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D125">
+        <v>7</v>
+      </c>
+      <c r="E125">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C126" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D126">
+        <v>6</v>
+      </c>
+      <c r="E126">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B127" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C127" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D127">
+        <v>8</v>
+      </c>
+      <c r="E127">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B128" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C128" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D128">
+        <v>9</v>
+      </c>
+      <c r="E128">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B129" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C129" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D129">
+        <v>4</v>
+      </c>
+      <c r="E129">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C130" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D130">
+        <v>4</v>
+      </c>
+      <c r="E130">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B131" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C131" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D131">
+        <v>4</v>
+      </c>
+      <c r="E131">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B132" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C132" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D132">
+        <v>6</v>
+      </c>
+      <c r="E132">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B133" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C133" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D133">
+        <v>7</v>
+      </c>
+      <c r="E133">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B134" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C134" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D134">
+        <v>4</v>
+      </c>
+      <c r="E134">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B135" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C135" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D135">
+        <v>6</v>
+      </c>
+      <c r="E135">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B136" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C136" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D136">
+        <v>4</v>
+      </c>
+      <c r="E136">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C137" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D137">
+        <v>5</v>
+      </c>
+      <c r="E137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C138" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D138">
+        <v>9</v>
+      </c>
+      <c r="E138">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C139" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D139">
+        <v>3</v>
+      </c>
+      <c r="E139">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B140" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C140" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D140">
+        <v>5</v>
+      </c>
+      <c r="E140">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B141" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C141" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D141">
+        <v>4</v>
+      </c>
+      <c r="E141">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C142" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D142">
+        <v>6</v>
+      </c>
+      <c r="E142">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B143" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C143" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D143">
+        <v>10</v>
+      </c>
+      <c r="E143">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B144" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C144" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D144">
+        <v>7</v>
+      </c>
+      <c r="E144">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B145" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C145" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D145">
+        <v>7</v>
+      </c>
+      <c r="E145">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B146" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C146" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D146">
+        <v>5</v>
+      </c>
+      <c r="E146">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B147" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C147" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D147">
+        <v>9</v>
+      </c>
+      <c r="E147">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B148" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C148" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D148">
+        <v>8</v>
+      </c>
+      <c r="E148">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B149" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C149" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D149">
+        <v>2</v>
+      </c>
+      <c r="E149">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C150" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C151" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D151">
+        <v>2</v>
+      </c>
+      <c r="E151">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C152" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D152">
+        <v>8</v>
+      </c>
+      <c r="E152">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C153" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D153">
+        <v>7</v>
+      </c>
+      <c r="E153">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B154" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C154" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D154">
+        <v>5</v>
+      </c>
+      <c r="E154">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B155" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C155" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D155">
+        <v>4</v>
+      </c>
+      <c r="E155">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B156" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C156" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D156">
+        <v>4</v>
+      </c>
+      <c r="E156">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B157" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C157" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D157">
+        <v>9</v>
+      </c>
+      <c r="E157">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B158" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C158" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D158">
+        <v>11</v>
+      </c>
+      <c r="E158">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B159" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C159" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D159">
+        <v>4</v>
+      </c>
+      <c r="E159">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C160" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D160">
+        <v>4</v>
+      </c>
+      <c r="E160">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B161" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="C161" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D161">
+        <v>4</v>
+      </c>
+      <c r="E161">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B162" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C162" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D162">
+        <v>8</v>
+      </c>
+      <c r="E162">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C163" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D163">
+        <v>12</v>
+      </c>
+      <c r="E163">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B164" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C164" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D164">
+        <v>8</v>
+      </c>
+      <c r="E164">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B165" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C165" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D165">
+        <v>6</v>
+      </c>
+      <c r="E165">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B166" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C166" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D166">
+        <v>8</v>
+      </c>
+      <c r="E166">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B167" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C167" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D167">
+        <v>10</v>
+      </c>
+      <c r="E167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B168" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C168" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D168">
+        <v>6</v>
+      </c>
+      <c r="E168">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B169" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C169" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D169">
+        <v>4</v>
+      </c>
+      <c r="E169">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B170" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C170" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D170">
+        <v>5</v>
+      </c>
+      <c r="E170">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B171" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C171" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D171">
+        <v>5</v>
+      </c>
+      <c r="E171">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B172" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C172" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D172">
+        <v>7</v>
+      </c>
+      <c r="E172">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B173" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C173" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D173">
+        <v>11</v>
+      </c>
+      <c r="E173">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B174" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C174" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D174">
+        <v>4</v>
+      </c>
+      <c r="E174">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B175" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C175" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D175">
+        <v>6</v>
+      </c>
+      <c r="E175">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B176" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C176" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D176">
+        <v>6</v>
+      </c>
+      <c r="E176">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B177" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C177" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D177">
+        <v>5</v>
+      </c>
+      <c r="E177">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B178" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C178" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D178">
+        <v>8</v>
+      </c>
+      <c r="E178">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B179" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C179" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D179">
+        <v>5</v>
+      </c>
+      <c r="E179">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B180" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C180" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D180">
+        <v>4</v>
+      </c>
+      <c r="E180">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B181" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C181" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D181">
+        <v>6</v>
+      </c>
+      <c r="E181">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B182" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C182" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D182">
+        <v>7</v>
+      </c>
+      <c r="E182">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B183" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C183" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D183">
+        <v>10</v>
+      </c>
+      <c r="E183">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B184" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C184" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D184">
+        <v>6</v>
+      </c>
+      <c r="E184">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B185" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C185" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D185">
+        <v>6</v>
+      </c>
+      <c r="E185">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B186" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C186" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D186">
+        <v>5</v>
+      </c>
+      <c r="E186">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B187" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C187" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D187">
+        <v>8</v>
+      </c>
+      <c r="E187">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B188" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C188" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D188">
+        <v>4</v>
+      </c>
+      <c r="E188">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B189" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C189" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D189">
+        <v>2</v>
+      </c>
+      <c r="E189">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B190" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C190" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D190">
+        <v>2</v>
+      </c>
+      <c r="E190">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B191" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C191" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B192" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C192" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D192">
+        <v>7</v>
+      </c>
+      <c r="E192">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B193" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C193" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D193">
+        <v>7</v>
+      </c>
+      <c r="E193">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B194" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C194" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D194">
+        <v>4</v>
+      </c>
+      <c r="E194">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B195" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C195" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D195">
+        <v>4</v>
+      </c>
+      <c r="E195">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B196" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C196" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D196">
+        <v>4</v>
+      </c>
+      <c r="E196">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B197" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C197" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D197">
+        <v>8</v>
+      </c>
+      <c r="E197">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B198" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C198" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D198">
+        <v>10</v>
+      </c>
+      <c r="E198">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B199" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C199" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D199">
+        <v>5</v>
+      </c>
+      <c r="E199">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B200" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C200" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D200">
+        <v>6</v>
+      </c>
+      <c r="E200">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B201" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="C201" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D201">
+        <v>6</v>
+      </c>
+      <c r="E201">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B202" t="str">
         <v>2025-12</v>
       </c>
-      <c r="C73">
-        <v>143</v>
-      </c>
-      <c r="D73">
-        <v>245</v>
-      </c>
-      <c r="E73">
-        <v>117</v>
-      </c>
-      <c r="F73">
+      <c r="C202" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B203" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C203" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D203">
+        <v>13</v>
+      </c>
+      <c r="E203">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B204" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C204" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D204">
+        <v>10</v>
+      </c>
+      <c r="E204">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B205" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C205" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D205">
+        <v>7</v>
+      </c>
+      <c r="E205">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>城东厅</v>
+      </c>
+      <c r="B206" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C206" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D206">
+        <v>10</v>
+      </c>
+      <c r="E206">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B207" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C207" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D207">
+        <v>10</v>
+      </c>
+      <c r="E207">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B208" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C208" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D208">
+        <v>8</v>
+      </c>
+      <c r="E208">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B209" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C209" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D209">
         <v>5</v>
       </c>
-      <c r="G73">
-        <v>1.29</v>
+      <c r="E209">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B210" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C210" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D210">
+        <v>3</v>
+      </c>
+      <c r="E210">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>城西厅</v>
+      </c>
+      <c r="B211" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C211" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D211">
+        <v>5</v>
+      </c>
+      <c r="E211">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B212" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C212" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D212">
+        <v>8</v>
+      </c>
+      <c r="E212">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B213" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C213" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D213">
+        <v>9</v>
+      </c>
+      <c r="E213">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B214" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C214" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D214">
+        <v>5</v>
+      </c>
+      <c r="E214">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B215" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C215" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+      <c r="E215">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>城南厅</v>
+      </c>
+      <c r="B216" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C216" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D216">
+        <v>4</v>
+      </c>
+      <c r="E216">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B217" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C217" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D217">
+        <v>8</v>
+      </c>
+      <c r="E217">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B218" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C218" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D218">
+        <v>10</v>
+      </c>
+      <c r="E218">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B219" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C219" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D219">
+        <v>6</v>
+      </c>
+      <c r="E219">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B220" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C220" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D220">
+        <v>4</v>
+      </c>
+      <c r="E220">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>城北厅</v>
+      </c>
+      <c r="B221" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C221" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D221">
+        <v>4</v>
+      </c>
+      <c r="E221">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B222" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C222" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D222">
+        <v>8</v>
+      </c>
+      <c r="E222">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B223" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C223" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D223">
+        <v>10</v>
+      </c>
+      <c r="E223">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B224" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C224" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D224">
+        <v>7</v>
+      </c>
+      <c r="E224">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B225" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C225" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D225">
+        <v>5</v>
+      </c>
+      <c r="E225">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>高新区厅</v>
+      </c>
+      <c r="B226" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C226" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D226">
+        <v>7</v>
+      </c>
+      <c r="E226">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B227" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C227" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D227">
+        <v>9</v>
+      </c>
+      <c r="E227">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B228" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C228" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D228">
+        <v>5</v>
+      </c>
+      <c r="E228">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B229" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C229" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D229">
+        <v>2</v>
+      </c>
+      <c r="E229">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B230" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C230" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D230">
+        <v>2</v>
+      </c>
+      <c r="E230">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>老城厅</v>
+      </c>
+      <c r="B231" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C231" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+      <c r="E231">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B232" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C232" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D232">
+        <v>7</v>
+      </c>
+      <c r="E232">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B233" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C233" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D233">
+        <v>8</v>
+      </c>
+      <c r="E233">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B234" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C234" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D234">
+        <v>6</v>
+      </c>
+      <c r="E234">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B235" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C235" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D235">
+        <v>4</v>
+      </c>
+      <c r="E235">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>滨江厅</v>
+      </c>
+      <c r="B236" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C236" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D236">
+        <v>6</v>
+      </c>
+      <c r="E236">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B237" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C237" t="str">
+        <v>装维服务</v>
+      </c>
+      <c r="D237">
+        <v>10</v>
+      </c>
+      <c r="E237">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B238" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C238" t="str">
+        <v>网络质量</v>
+      </c>
+      <c r="D238">
+        <v>9</v>
+      </c>
+      <c r="E238">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B239" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C239" t="str">
+        <v>资费争议</v>
+      </c>
+      <c r="D239">
+        <v>7</v>
+      </c>
+      <c r="E239">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B240" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C240" t="str">
+        <v>业务办理</v>
+      </c>
+      <c r="D240">
+        <v>5</v>
+      </c>
+      <c r="E240">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>中心厅</v>
+      </c>
+      <c r="B241" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="C241" t="str">
+        <v>其他</v>
+      </c>
+      <c r="D241">
+        <v>5</v>
+      </c>
+      <c r="E241">
+        <v>5.3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G73"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E241"/>
   </ignoredErrors>
 </worksheet>
 </file>